--- a/Adapters/adapter_support_matrix.xlsx
+++ b/Adapters/adapter_support_matrix.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -89,6 +94,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -462,6 +470,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="110" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,6 +528,11 @@
           <t>notes / quirks</t>
         </is>
       </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>repository check (2026-10-09, static; no test executed)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -546,6 +560,11 @@
           <t>founding family</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list (transformer_lens/supported_models.py). Bridge registry: listed as openai-community/gpt2, verified.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -573,6 +592,11 @@
           <t>revision-pinned</t>
         </is>
       </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (GPTNeoXForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -600,6 +624,11 @@
           <t>RMSNorm, RoPE</t>
         </is>
       </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (LlamaForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -627,6 +656,11 @@
           <t>GQA, scaled RoPE</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (LlamaForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -654,6 +688,11 @@
           <t>MoE routing, interleaved RoPE; RunPod test</t>
         </is>
       </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>CONTRADICTED BY REPO: checkpoint is in neither the HookedTransformer list nor the Bridge registry; Llama4ForCausalLM and Llama4ForConditionalGeneration are listed as unsupported in architecture_gaps.json.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -681,6 +720,11 @@
           <t>tied embeddings</t>
         </is>
       </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (Qwen2ForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -708,6 +752,11 @@
           <t>vision tower out of scope; text stack only</t>
         </is>
       </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>CONTRADICTED BY REPO: checkpoint is in neither list; Qwen2_5_VLForConditionalGeneration is listed as unsupported in architecture_gaps.json.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -735,6 +784,11 @@
           <t>QK-norm; #1078</t>
         </is>
       </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (Qwen3ForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -762,6 +816,11 @@
           <t>sliding-window attn; #1075</t>
         </is>
       </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>NOT CONFIRMED: no checkpoint with this exact id in either list. mistralai/Mistral-Small-24B-Base-2501 is in the HookedTransformer list and untested in the Bridge registry; Mistral3ForConditionalGeneration is listed as unsupported.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -789,6 +848,11 @@
           <t>logit soft-cap</t>
         </is>
       </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: verified (Gemma2ForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -816,6 +880,11 @@
           <t>norm-eps fix in 2.16.1; #1112/#1121</t>
         </is>
       </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>ID MISMATCH: no 'google/gemma-3-1b' in either list. google/gemma-3-1b-it and -pt are in the HookedTransformer list and verified in the Bridge registry.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -843,6 +912,11 @@
           <t>partial RoPE</t>
         </is>
       </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>ID MISMATCH: no 'microsoft/Phi-3-mini-4k' in either list. microsoft/Phi-3-mini-4k-instruct is in the HookedTransformer list and verified in the Bridge registry.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -870,6 +944,11 @@
           <t>parallel attn/MLP</t>
         </is>
       </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Checkpoint is in the HookedTransformer list. Bridge registry: skipped, never verified (GPTNeoXForCausalLM).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -897,6 +976,11 @@
           <t>parallel attn/MLP, logit_scale 1/16, adjacent-pair (interleaved) RoPE, GQA; QK-norm on Command-R+. Acceptance test written but NOT RUN (no torch / Hub access where it was written); pass/fail: none recorded. This checkpoint FAILED parity in the registry before the RoPE fix (P1=50%, 2026-06-26). Test runs through TransformerBridge: no HookedTransformer implementation exists for Cohere. Official checkpoints are gated. #1124; see docs/source/content/release_readiness.md</t>
         </is>
       </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Adapter cohere.py registered as CohereForCausalLM. Not in the HookedTransformer list. Bridge registry for this checkpoint: FAILED (P1=50%). 1 of 19 Cohere entries verified (a d_head=2 model), 1 failed, 17 skipped.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -924,6 +1008,11 @@
           <t>MLA + MoE; adapter deepseek_v2.py. Registry: 0 verified, 1 failed (this checkpoint, P1=0%), 29 skipped. No acceptance pass recorded. #1127</t>
         </is>
       </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Adapter deepseek_v2.py registered as DeepseekV2ForCausalLM. Bridge registry for this checkpoint: FAILED (P1=0%). 0 of 30 entries verified.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -951,6 +1040,11 @@
           <t>MLA + MoE; adapter deepseek_v3.py. Registry: 2 tiny random models verified with issues (P3=89.5%), 5 tiny models failed P1, 53 skipped; no full-size checkpoint has run. #1127</t>
         </is>
       </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Adapter deepseek_v3.py registered as DeepseekV3ForCausalLM. Bridge registry for this checkpoint: verified with issues (P1=100%, P3=89.5%). 2 of 60 entries verified, 5 failed, 53 skipped.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -978,6 +1072,11 @@
           <t>No separate adapter: R1 loads through the DeepSeek V3 adapter. 0 of 10 R1-named V3 registry entries verified (all skipped). R1 distillations are Qwen-2.5 / LLaMA models, not this adapter. #1127</t>
         </is>
       </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No R1-specific adapter or factory key. deepseek-ai/DeepSeek-R1 is a DeepseekV3ForCausalLM entry in the Bridge registry: skipped (too large).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1005,6 +1104,11 @@
           <t>Cohere2ForCausalLM has no adapter in this repository (listed in architecture_gaps.json, 27 models). Upstream TransformerLens dev has one.</t>
         </is>
       </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>No Cohere2 adapter or factory key. Cohere2ForCausalLM and Cohere2MoeForCausalLM are listed in architecture_gaps.json.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1030,6 +1134,11 @@
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>DeepseekV32ForCausalLM and DeepseekV4ForCausalLM have no adapter (listed in architecture_gaps.json, 15 and 52 models).</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>No adapter or factory key. DeepseekV32ForCausalLM and DeepseekV4ForCausalLM are listed in architecture_gaps.json.</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1227,7 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Copied unchanged on 2026-10-09 from the Drive sheet 'Model-adapater support matrix.xlsx'; not re-verified against this repository.</t>
+          <t>Columns A-E copied unchanged on 2026-10-09 from the Drive sheet 'Model-adapater support matrix.xlsx'. Their acceptance-test results were not verified. Column F records what this repository shows for each row; shaded cells disagree with the row.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1242,7 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Added 2026-10-09 from this repository's adapter code and transformer_lens/tools/model_registry/data/supported_models.json (generated 2026-06-25). Nothing was executed.</t>
+          <t>Added 2026-10-09 from this repository's adapter code, transformer_lens/tools/model_registry/data/supported_models.json (generated 2026-06-25) and architecture_gaps.json. Nothing was executed.</t>
         </is>
       </c>
     </row>

--- a/Adapters/adapter_support_matrix.xlsx
+++ b/Adapters/adapter_support_matrix.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>parallel attn/MLP, logit_scale 1/16, adjacent-pair (interleaved) RoPE, GQA; QK-norm on Command-R+. Acceptance test written but NOT RUN (no torch / Hub access where it was written); pass/fail: none recorded. This checkpoint FAILED parity in the registry before the RoPE fix (P1=50%, 2026-06-26). Test runs through TransformerBridge: no HookedTransformer implementation exists for Cohere. Official checkpoints are gated. #1124; see docs/source/content/release_readiness.md</t>
+          <t>parallel attn/MLP, logit_scale 1/16, adjacent-pair (interleaved) RoPE, GQA; QK-norm on Command-R+. Acceptance test written but NOT RUN (no torch / Hub access where it was written); pass/fail: none recorded. Run with: make cohere-acceptance-test. This checkpoint FAILED parity in the registry before the RoPE fix (P1=50%, 2026-06-26). Test runs through TransformerBridge: no HookedTransformer implementation exists for Cohere. Official checkpoints are gated. #1124; see docs/source/content/release_readiness.md</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
